--- a/web/Pipistrelli 2024.xlsx
+++ b/web/Pipistrelli 2024.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,9 +48,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -493,7 +493,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>45303</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,7 +539,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
         <v>45.6413213</v>
       </c>
@@ -553,7 +552,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>45334</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,7 +565,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>San Lazzaro</t>
@@ -595,7 +593,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
         <v>45.7483873</v>
       </c>
@@ -609,7 +606,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>45371</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -622,7 +619,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -651,7 +647,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
         <v>45.6348591</v>
       </c>
@@ -665,7 +660,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>45385</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -711,7 +706,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
         <v>45.6348591</v>
       </c>
@@ -725,7 +719,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>45388</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -771,17 +765,20 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
         <v>45.6111057</v>
       </c>
       <c r="M6" t="n">
         <v>11.3434053</v>
       </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>45389</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -827,17 +824,20 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
         <v>45.6111057</v>
       </c>
       <c r="M7" t="n">
         <v>11.3434053</v>
       </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>45395</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -883,7 +883,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
         <v>45.772805</v>
       </c>
@@ -897,7 +896,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>45397</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -943,7 +942,6 @@
           <t>in degenza</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
         <v>45.5084288</v>
       </c>
@@ -957,7 +955,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>45398</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -970,7 +968,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t xml:space="preserve">Grisignano </t>
@@ -999,17 +996,15 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
         <v>44.1821589</v>
       </c>
       <c r="M10" t="n">
         <v>12.0321866</v>
       </c>
-      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>45422</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -1022,7 +1017,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -1051,7 +1045,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
         <v>45.6348591</v>
       </c>
@@ -1065,7 +1058,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>45423</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -1111,17 +1104,20 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
         <v>45.8461561</v>
       </c>
       <c r="M12" t="n">
         <v>11.3017652</v>
       </c>
-      <c r="N12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>45429</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -1167,7 +1163,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
         <v>45.7669109</v>
       </c>
@@ -1181,7 +1176,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>45429</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -1194,7 +1189,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Viale Sant'Agostino</t>
@@ -1223,7 +1217,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
         <v>45.5276929</v>
       </c>
@@ -1237,7 +1230,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>45434</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -1283,17 +1276,15 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
         <v>45.5063765</v>
       </c>
       <c r="M15" t="n">
         <v>11.5093217</v>
       </c>
-      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>45436</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -1306,7 +1297,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>Viale della Pace</t>
@@ -1335,7 +1325,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
         <v>45.5419084</v>
       </c>
@@ -1349,7 +1338,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>45437</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -1395,7 +1384,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
         <v>45.8066913</v>
       </c>
@@ -1409,7 +1397,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>45446</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -1422,7 +1410,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>Lago di Fimon</t>
@@ -1451,17 +1438,15 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
         <v>45.4711586</v>
       </c>
       <c r="M18" t="n">
         <v>11.5436596</v>
       </c>
-      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>45446</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -1474,7 +1459,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>Lago di Fimon</t>
@@ -1503,17 +1487,15 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
         <v>45.4711586</v>
       </c>
       <c r="M19" t="n">
         <v>11.5436596</v>
       </c>
-      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>45460</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -1526,7 +1508,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>Arcugnano</t>
@@ -1555,17 +1536,20 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
         <v>45.5004723</v>
       </c>
       <c r="M20" t="n">
         <v>11.5356994</v>
       </c>
-      <c r="N20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>45460</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -1578,7 +1562,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>Via Col d'Echele 3</t>
@@ -1607,7 +1590,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
         <v>45.5561119</v>
       </c>
@@ -1621,7 +1603,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>45460</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -1634,7 +1616,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>Grisignano</t>
@@ -1663,17 +1644,15 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
         <v>44.1821589</v>
       </c>
       <c r="M22" t="n">
         <v>12.0321866</v>
       </c>
-      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>45462</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -1686,7 +1665,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>Arzignano</t>
@@ -1715,7 +1693,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
         <v>45.519292</v>
       </c>
@@ -1729,7 +1706,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>45462</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -1742,7 +1719,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t xml:space="preserve">Castegnero </t>
@@ -1771,17 +1747,20 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
         <v>45.4424748</v>
       </c>
       <c r="M24" t="n">
         <v>11.5844477</v>
       </c>
-      <c r="N24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>45462</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -1794,7 +1773,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t xml:space="preserve">Castegnero </t>
@@ -1823,17 +1801,20 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
         <v>45.4424748</v>
       </c>
       <c r="M25" t="n">
         <v>11.5844477</v>
       </c>
-      <c r="N25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>45462</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -1846,7 +1827,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>Verona</t>
@@ -1875,7 +1855,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
         <v>45.4424977</v>
       </c>
@@ -1889,7 +1868,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>45462</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -1902,7 +1881,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>Schio</t>
@@ -1947,7 +1925,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>45463</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -1960,7 +1938,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>Thiene</t>
@@ -1989,7 +1966,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
         <v>45.7059893</v>
       </c>
@@ -2003,7 +1979,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>45464</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -2049,17 +2025,20 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
         <v>45.5951803</v>
       </c>
       <c r="M29" t="n">
         <v>11.5805788</v>
       </c>
-      <c r="N29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>45464</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -2072,7 +2051,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>Schio</t>
@@ -2101,7 +2079,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
       <c r="L30" t="n">
         <v>45.7113511</v>
       </c>
@@ -2115,7 +2092,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>45465</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -2128,7 +2105,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>Piovene Rocchette</t>
@@ -2157,17 +2133,20 @@
           <t>in degenza</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
         <v>45.7588257</v>
       </c>
       <c r="M31" t="n">
         <v>11.4301268</v>
       </c>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>45466</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -2180,7 +2159,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>Costozza</t>
@@ -2218,10 +2196,14 @@
       <c r="M32" t="n">
         <v>11.6014322</v>
       </c>
-      <c r="N32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>45467</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -2234,7 +2216,6 @@
           <t>Pipistrellus pipistrellus</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>via giustiniani 79</t>
@@ -2263,17 +2244,20 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
       <c r="L33" t="n">
         <v>45.5056451</v>
       </c>
       <c r="M33" t="n">
         <v>11.5081895</v>
       </c>
-      <c r="N33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>45467</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -2286,7 +2270,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t xml:space="preserve">montecchio </t>
@@ -2331,7 +2314,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>45467</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -2377,17 +2360,20 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
       <c r="L35" t="n">
         <v>45.5220266</v>
       </c>
       <c r="M35" t="n">
         <v>11.7134998</v>
       </c>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>45467</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -2433,17 +2419,20 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
       <c r="L36" t="n">
         <v>45.5220266</v>
       </c>
       <c r="M36" t="n">
         <v>11.7134998</v>
       </c>
-      <c r="N36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>45467</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -2456,7 +2445,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>Verona</t>
@@ -2485,7 +2473,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
       <c r="L37" t="n">
         <v>45.4424977</v>
       </c>
@@ -2499,7 +2486,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>45467</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -2512,7 +2499,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
           <t>Corso Santi Felice e Fortunato</t>
@@ -2550,10 +2536,9 @@
       <c r="M38" t="n">
         <v>11.5352125</v>
       </c>
-      <c r="N38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>45467</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -2566,7 +2551,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>Via Marchetti, 14</t>
@@ -2611,7 +2595,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>45467</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -2624,7 +2608,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>Costozza</t>
@@ -2653,17 +2636,15 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
         <v>45.4709699</v>
       </c>
       <c r="M40" t="n">
         <v>11.6014322</v>
       </c>
-      <c r="N40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>45468</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -2676,7 +2657,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>Via Leonardo da Vinci, 8</t>
@@ -2705,17 +2685,20 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
       <c r="L41" t="n">
         <v>45.6577391</v>
       </c>
       <c r="M41" t="n">
         <v>11.5831095</v>
       </c>
-      <c r="N41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>45468</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -2728,7 +2711,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>Pove del Grappa</t>
@@ -2757,17 +2739,20 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
       <c r="L42" t="n">
         <v>45.7991169</v>
       </c>
       <c r="M42" t="n">
         <v>11.7291016</v>
       </c>
-      <c r="N42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>45468</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -2813,7 +2798,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
       <c r="L43" t="n">
         <v>45.697721</v>
       </c>
@@ -2827,7 +2811,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>45468</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -2840,7 +2824,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>Costozza</t>
@@ -2878,10 +2861,9 @@
       <c r="M44" t="n">
         <v>11.6014322</v>
       </c>
-      <c r="N44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>45469</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -2894,7 +2876,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>Via Giuseppe Roi, 13</t>
@@ -2923,17 +2904,20 @@
           <t>in degenza</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
       <c r="L45" t="n">
         <v>45.4558599</v>
       </c>
       <c r="M45" t="n">
         <v>11.6526775</v>
       </c>
-      <c r="N45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>45470</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -2946,7 +2930,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>Via Piave 23</t>
@@ -2975,17 +2958,20 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
       <c r="L46" t="n">
         <v>45.6180489</v>
       </c>
       <c r="M46" t="n">
         <v>11.4651626</v>
       </c>
-      <c r="N46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>45470</v>
       </c>
       <c r="B47" t="inlineStr">
@@ -2998,7 +2984,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>Via Don A. Ziliotto, 24</t>
@@ -3017,13 +3002,11 @@
       <c r="H47" t="n">
         <v>1</v>
       </c>
-      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>liberato</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
       <c r="L47" t="n">
         <v>45.7059893</v>
       </c>
@@ -3037,7 +3020,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>45470</v>
       </c>
       <c r="B48" t="inlineStr">
@@ -3050,7 +3033,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -3095,7 +3077,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>45470</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -3108,7 +3090,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>Bassano del Grappa, Vicenza</t>
@@ -3137,7 +3118,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
       <c r="L49" t="n">
         <v>45.7669109</v>
       </c>
@@ -3151,7 +3131,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45471</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -3164,7 +3144,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -3209,7 +3188,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45471</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -3222,7 +3201,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>Via Scomazzoni 12A</t>
@@ -3267,7 +3245,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45471</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -3280,7 +3258,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>Via Monsinior Pertile</t>
@@ -3309,7 +3286,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
       <c r="L52" t="n">
         <v>45.7059893</v>
       </c>
@@ -3323,7 +3299,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45471</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -3336,7 +3312,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>Via Nicolò Tommaso 12</t>
@@ -3365,17 +3340,20 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
       <c r="L53" t="n">
         <v>45.6861778</v>
       </c>
       <c r="M53" t="n">
         <v>11.7041837</v>
       </c>
-      <c r="N53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45471</v>
       </c>
       <c r="B54" t="inlineStr">
@@ -3388,7 +3366,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>Via Andrea Boccherini 23</t>
@@ -3433,7 +3410,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45471</v>
       </c>
       <c r="B55" t="inlineStr">
@@ -3446,7 +3423,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>Via Monsignor Pertile</t>
@@ -3475,7 +3451,6 @@
           <t>in degenza</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
       <c r="L55" t="n">
         <v>45.7059893</v>
       </c>
@@ -3489,7 +3464,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45471</v>
       </c>
       <c r="B56" t="inlineStr">
@@ -3535,7 +3510,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
       <c r="L56" t="n">
         <v>45.5502771</v>
       </c>
@@ -3549,7 +3523,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45472</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -3562,7 +3536,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>Via Lago di Tovel, 43</t>
@@ -3607,7 +3580,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45472</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -3620,7 +3593,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>Monselice</t>
@@ -3665,7 +3637,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45472</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -3678,7 +3650,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>Thiene</t>
@@ -3723,7 +3694,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45472</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -3736,7 +3707,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>Grisignano</t>
@@ -3774,10 +3744,9 @@
       <c r="M60" t="n">
         <v>12.0321866</v>
       </c>
-      <c r="N60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -3790,7 +3759,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>brogliano</t>
@@ -3819,17 +3787,20 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
       <c r="L61" t="n">
         <v>45.5887862</v>
       </c>
       <c r="M61" t="n">
         <v>11.3645426</v>
       </c>
-      <c r="N61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -3842,7 +3813,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t xml:space="preserve">Isola Vicentina </t>
@@ -3871,17 +3841,20 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
       <c r="L62" t="n">
         <v>45.6286685</v>
       </c>
       <c r="M62" t="n">
         <v>11.4431478</v>
       </c>
-      <c r="N62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B63" t="inlineStr">
@@ -3894,7 +3867,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>Marostica</t>
@@ -3923,7 +3895,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
       <c r="L63" t="n">
         <v>45.7453924</v>
       </c>
@@ -3937,7 +3908,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B64" t="inlineStr">
@@ -3950,7 +3921,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>Sovizzo</t>
@@ -3979,17 +3949,20 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
       <c r="L64" t="n">
         <v>45.5280283</v>
       </c>
       <c r="M64" t="n">
         <v>11.4456338</v>
       </c>
-      <c r="N64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B65" t="inlineStr">
@@ -4002,7 +3975,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>Sovizzo</t>
@@ -4031,17 +4003,20 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
       <c r="L65" t="n">
         <v>45.5280283</v>
       </c>
       <c r="M65" t="n">
         <v>11.4456338</v>
       </c>
-      <c r="N65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B66" t="inlineStr">
@@ -4054,7 +4029,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>Altavilla vicentina</t>
@@ -4099,7 +4073,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B67" t="inlineStr">
@@ -4112,7 +4086,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>Bressanvido</t>
@@ -4141,17 +4114,20 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
       <c r="L67" t="n">
         <v>45.6459759</v>
       </c>
       <c r="M67" t="n">
         <v>11.6329987</v>
       </c>
-      <c r="N67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45475</v>
       </c>
       <c r="B68" t="inlineStr">
@@ -4164,7 +4140,6 @@
           <t>Pipistrellus kuhlii</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>Treviso</t>
@@ -4193,7 +4168,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
       <c r="L68" t="n">
         <v>45.8066913</v>
       </c>
@@ -4207,7 +4181,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45475</v>
       </c>
       <c r="B69" t="inlineStr">
@@ -4220,7 +4194,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>Via Jacopo da Ponte</t>
@@ -4249,17 +4222,20 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
       <c r="L69" t="n">
         <v>45.6230008</v>
       </c>
       <c r="M69" t="n">
         <v>11.5745789</v>
       </c>
-      <c r="N69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B70" t="inlineStr">
@@ -4272,7 +4248,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>Via Monsignor Pertile</t>
@@ -4301,7 +4276,6 @@
           <t>in degenza</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
       <c r="L70" t="n">
         <v>45.7059893</v>
       </c>
@@ -4315,7 +4289,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45475</v>
       </c>
       <c r="B71" t="inlineStr">
@@ -4328,7 +4302,6 @@
           <t>Pipistrellus sp.</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>Schio</t>
@@ -4357,7 +4330,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
       <c r="L71" t="n">
         <v>45.7113511</v>
       </c>
@@ -4371,7 +4343,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>45475</v>
       </c>
       <c r="B72" t="inlineStr">
@@ -4384,7 +4356,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>via bologna 33</t>
@@ -4413,7 +4384,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
       <c r="L72" t="n">
         <v>45.515467</v>
       </c>
@@ -4427,7 +4397,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>45476</v>
       </c>
       <c r="B73" t="inlineStr">
@@ -4440,7 +4410,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>Arcugnano</t>
@@ -4469,17 +4438,20 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
       <c r="L73" t="n">
         <v>45.5004723</v>
       </c>
       <c r="M73" t="n">
         <v>11.5356994</v>
       </c>
-      <c r="N73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>45478</v>
       </c>
       <c r="B74" t="inlineStr">
@@ -4492,7 +4464,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>Viale della Pace</t>
@@ -4521,7 +4492,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
       <c r="L74" t="n">
         <v>45.5419084</v>
       </c>
@@ -4535,7 +4505,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>45479</v>
       </c>
       <c r="B75" t="inlineStr">
@@ -4548,7 +4518,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>vicenza</t>
@@ -4577,7 +4546,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
       <c r="L75" t="n">
         <v>45.6348591</v>
       </c>
@@ -4591,7 +4559,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>45481</v>
       </c>
       <c r="B76" t="inlineStr">
@@ -4604,7 +4572,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>Camisano</t>
@@ -4633,17 +4600,20 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
       <c r="L76" t="n">
         <v>45.443275</v>
       </c>
       <c r="M76" t="n">
         <v>9.745760000000001</v>
       </c>
-      <c r="N76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>45481</v>
       </c>
       <c r="B77" t="inlineStr">
@@ -4656,7 +4626,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>Strada statale Pasubio</t>
@@ -4694,10 +4663,14 @@
       <c r="M77" t="n">
         <v>11.4877438</v>
       </c>
-      <c r="N77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>45481</v>
       </c>
       <c r="B78" t="inlineStr">
@@ -4710,7 +4683,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>Valdagno</t>
@@ -4755,7 +4727,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>45481</v>
       </c>
       <c r="B79" t="inlineStr">
@@ -4768,7 +4740,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>Via canestrello 8</t>
@@ -4797,17 +4768,20 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
       <c r="L79" t="n">
         <v>45.5548982</v>
       </c>
       <c r="M79" t="n">
         <v>11.4719785</v>
       </c>
-      <c r="N79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>45481</v>
       </c>
       <c r="B80" t="inlineStr">
@@ -4820,7 +4794,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>Via gioranzan 13</t>
@@ -4849,17 +4822,20 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
       <c r="L80" t="n">
         <v>45.5208426</v>
       </c>
       <c r="M80" t="n">
         <v>11.6905167</v>
       </c>
-      <c r="N80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>45482</v>
       </c>
       <c r="B81" t="inlineStr">
@@ -4872,7 +4848,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>Via Carlesse 55</t>
@@ -4901,17 +4876,20 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
       <c r="L81" t="n">
         <v>45.636598</v>
       </c>
       <c r="M81" t="n">
         <v>11.5422153</v>
       </c>
-      <c r="N81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>45482</v>
       </c>
       <c r="B82" t="inlineStr">
@@ -4924,7 +4902,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
           <t>Cornedo Vicentino</t>
@@ -4962,10 +4939,14 @@
       <c r="M82" t="n">
         <v>11.3434053</v>
       </c>
-      <c r="N82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>45482</v>
       </c>
       <c r="B83" t="inlineStr">
@@ -5011,17 +4992,20 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
       <c r="L83" t="n">
         <v>45.3317317</v>
       </c>
       <c r="M83" t="n">
         <v>11.5714548</v>
       </c>
-      <c r="N83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>45484</v>
       </c>
       <c r="B84" t="inlineStr">
@@ -5034,7 +5018,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>Santorso</t>
@@ -5079,7 +5062,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>45485</v>
       </c>
       <c r="B85" t="inlineStr">
@@ -5092,7 +5075,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>Povolaro</t>
@@ -5130,10 +5112,14 @@
       <c r="M85" t="n">
         <v>11.5733922</v>
       </c>
-      <c r="N85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>45486</v>
       </c>
       <c r="B86" t="inlineStr">
@@ -5146,7 +5132,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>Longare</t>
@@ -5175,17 +5160,20 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
       <c r="L86" t="n">
         <v>45.4746344</v>
       </c>
       <c r="M86" t="n">
         <v>11.6110489</v>
       </c>
-      <c r="N86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>45488</v>
       </c>
       <c r="B87" t="inlineStr">
@@ -5198,7 +5186,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>Via Oreficeria, 16</t>
@@ -5227,7 +5214,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
       <c r="L87" t="n">
         <v>45.5288639</v>
       </c>
@@ -5241,7 +5227,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>45490</v>
       </c>
       <c r="B88" t="inlineStr">
@@ -5254,7 +5240,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>Malga monte Asolone</t>
@@ -5283,17 +5268,20 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
       <c r="L88" t="n">
         <v>45.8672973</v>
       </c>
       <c r="M88" t="n">
         <v>11.741934</v>
       </c>
-      <c r="N88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>45490</v>
       </c>
       <c r="B89" t="inlineStr">
@@ -5306,7 +5294,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
           <t>Via Aurelio dall'acqua 119</t>
@@ -5335,7 +5322,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
       <c r="L89" t="n">
         <v>45.5678021</v>
       </c>
@@ -5349,7 +5335,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>45490</v>
       </c>
       <c r="B90" t="inlineStr">
@@ -5362,7 +5348,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>Via Tecchio</t>
@@ -5407,7 +5392,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>45490</v>
       </c>
       <c r="B91" t="inlineStr">
@@ -5420,7 +5405,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>Via Marnian</t>
@@ -5449,7 +5433,6 @@
           <t>in degenza</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
       <c r="L91" t="n">
         <v>45.7669109</v>
       </c>
@@ -5463,7 +5446,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>45492</v>
       </c>
       <c r="B92" t="inlineStr">
@@ -5476,7 +5459,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>Via mottarella 17</t>
@@ -5505,17 +5487,20 @@
           <t>in degenza</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
       <c r="L92" t="n">
         <v>45.3446852</v>
       </c>
       <c r="M92" t="n">
         <v>11.4583737</v>
       </c>
-      <c r="N92" t="inlineStr"/>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>45494</v>
       </c>
       <c r="B93" t="inlineStr">
@@ -5528,7 +5513,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
           <t>Vicolo xx settembre 9</t>
@@ -5557,7 +5541,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
       <c r="L93" t="n">
         <v>45.7683298</v>
       </c>
@@ -5571,7 +5554,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>45497</v>
       </c>
       <c r="B94" t="inlineStr">
@@ -5584,7 +5567,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>Bassano</t>
@@ -5629,7 +5611,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>45499</v>
       </c>
       <c r="B95" t="inlineStr">
@@ -5642,7 +5624,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
           <t>Calvene</t>
@@ -5671,17 +5652,20 @@
           <t>in degenza</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
       <c r="L95" t="n">
         <v>45.7659086</v>
       </c>
       <c r="M95" t="n">
         <v>11.5121486</v>
       </c>
-      <c r="N95" t="inlineStr"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>45502</v>
       </c>
       <c r="B96" t="inlineStr">
@@ -5694,7 +5678,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
           <t>Lusiana</t>
@@ -5723,17 +5706,15 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
       <c r="L96" t="n">
         <v>45.7851934</v>
       </c>
       <c r="M96" t="n">
         <v>11.576369</v>
       </c>
-      <c r="N96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>45503</v>
       </c>
       <c r="B97" t="inlineStr">
@@ -5746,7 +5727,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
           <t>Via dei laghi 20</t>
@@ -5775,7 +5755,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
       <c r="L97" t="n">
         <v>45.5211218</v>
       </c>
@@ -5789,7 +5768,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>45503</v>
       </c>
       <c r="B98" t="inlineStr">
@@ -5802,7 +5781,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
           <t>Via Barco 21</t>
@@ -5831,17 +5809,20 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
       <c r="L98" t="n">
         <v>45.6077149</v>
       </c>
       <c r="M98" t="n">
         <v>11.5097243</v>
       </c>
-      <c r="N98" t="inlineStr"/>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B99" t="inlineStr">
@@ -5854,7 +5835,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
           <t>Via odone 18 a</t>
@@ -5883,17 +5863,20 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
       <c r="L99" t="n">
         <v>47.2186371</v>
       </c>
       <c r="M99" t="n">
         <v>-1.5541362</v>
       </c>
-      <c r="N99" t="inlineStr"/>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B100" t="inlineStr">
@@ -5939,17 +5922,20 @@
           <t>in degenza</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
       <c r="L100" t="n">
         <v>45.7962374</v>
       </c>
       <c r="M100" t="n">
         <v>11.7583907</v>
       </c>
-      <c r="N100" t="inlineStr"/>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>45511</v>
       </c>
       <c r="B101" t="inlineStr">
@@ -5962,7 +5948,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>Valdagno</t>
@@ -5991,7 +5976,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
       <c r="L101" t="n">
         <v>45.6413213</v>
       </c>
@@ -6005,7 +5989,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>45520</v>
       </c>
       <c r="B102" t="inlineStr">
@@ -6018,7 +6002,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
           <t>Via monte oro 33</t>
@@ -6047,17 +6030,20 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
       <c r="L102" t="n">
         <v>45.7942477</v>
       </c>
       <c r="M102" t="n">
         <v>11.7321801</v>
       </c>
-      <c r="N102" t="inlineStr"/>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>45525</v>
       </c>
       <c r="B103" t="inlineStr">
@@ -6070,7 +6056,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
           <t>Valdagno</t>
@@ -6099,7 +6084,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
       <c r="L103" t="n">
         <v>45.6413213</v>
       </c>
@@ -6113,7 +6097,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>45533</v>
       </c>
       <c r="B104" t="inlineStr">
@@ -6159,7 +6143,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
       <c r="L104" t="n">
         <v>45.7669109</v>
       </c>
@@ -6173,7 +6156,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>45533</v>
       </c>
       <c r="B105" t="inlineStr">
@@ -6186,7 +6169,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
           <t>Via Marco Marinoni 28</t>
@@ -6231,7 +6213,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>45537</v>
       </c>
       <c r="B106" t="inlineStr">
@@ -6244,7 +6226,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -6273,7 +6254,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
       <c r="L106" t="n">
         <v>45.6348591</v>
       </c>
@@ -6287,7 +6267,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>45540</v>
       </c>
       <c r="B107" t="inlineStr">
@@ -6300,7 +6280,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>Dueville</t>
@@ -6329,17 +6308,20 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
       <c r="L107" t="n">
         <v>45.6355174</v>
       </c>
       <c r="M107" t="n">
         <v>11.5485978</v>
       </c>
-      <c r="N107" t="inlineStr"/>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>45544</v>
       </c>
       <c r="B108" t="inlineStr">
@@ -6352,7 +6334,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
           <t>Via Oreficeria, 16</t>
@@ -6381,7 +6362,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
       <c r="L108" t="n">
         <v>45.5288639</v>
       </c>
@@ -6395,7 +6375,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>45544</v>
       </c>
       <c r="B109" t="inlineStr">
@@ -6408,7 +6388,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
           <t>Arcugnano</t>
@@ -6437,17 +6416,20 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
       <c r="L109" t="n">
         <v>45.5004723</v>
       </c>
       <c r="M109" t="n">
         <v>11.5356994</v>
       </c>
-      <c r="N109" t="inlineStr"/>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>45544</v>
       </c>
       <c r="B110" t="inlineStr">
@@ -6460,7 +6442,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
           <t>Via Monte Pasubio 96a</t>
@@ -6489,17 +6470,20 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
       <c r="L110" t="n">
         <v>45.7209364</v>
       </c>
       <c r="M110" t="n">
         <v>11.4422352</v>
       </c>
-      <c r="N110" t="inlineStr"/>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>45547</v>
       </c>
       <c r="B111" t="inlineStr">
@@ -6545,7 +6529,6 @@
           <t>in degenza</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
       <c r="L111" t="n">
         <v>45.5269679</v>
       </c>
@@ -6559,7 +6542,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>45552</v>
       </c>
       <c r="B112" t="inlineStr">
@@ -6572,7 +6555,6 @@
           <t>Plecotus sp.</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t xml:space="preserve">Bassano del Grappa </t>
@@ -6601,7 +6583,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
       <c r="L112" t="n">
         <v>45.7669109</v>
       </c>
@@ -6615,7 +6596,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>45553</v>
       </c>
       <c r="B113" t="inlineStr">
@@ -6628,7 +6609,6 @@
           <t>Plecotus Macrobullaris</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
           <t>Santorso</t>
@@ -6657,7 +6637,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
       <c r="L113" t="n">
         <v>45.7372986</v>
       </c>
@@ -6671,7 +6650,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>45556</v>
       </c>
       <c r="B114" t="inlineStr">
@@ -6717,7 +6696,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
       <c r="L114" t="n">
         <v>45.5419084</v>
       </c>
@@ -6731,7 +6709,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>45557</v>
       </c>
       <c r="B115" t="inlineStr">
@@ -6744,7 +6722,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
           <t>Via San Niccolò 53</t>
@@ -6763,23 +6740,20 @@
       <c r="H115" t="n">
         <v>1</v>
       </c>
-      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>in degenza</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
       <c r="L115" t="n">
         <v>45.453842</v>
       </c>
       <c r="M115" t="n">
         <v>11.5551735</v>
       </c>
-      <c r="N115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>45558</v>
       </c>
       <c r="B116" t="inlineStr">
@@ -6792,7 +6766,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
           <t xml:space="preserve">Dueville </t>
@@ -6821,17 +6794,20 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
       <c r="L116" t="n">
         <v>45.6355174</v>
       </c>
       <c r="M116" t="n">
         <v>11.5485978</v>
       </c>
-      <c r="N116" t="inlineStr"/>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>45560</v>
       </c>
       <c r="B117" t="inlineStr">
@@ -6877,7 +6853,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
       <c r="L117" t="n">
         <v>45.7059893</v>
       </c>
@@ -6891,7 +6866,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>45562</v>
       </c>
       <c r="B118" t="inlineStr">
@@ -6937,17 +6912,20 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
       <c r="L118" t="n">
         <v>45.6073305</v>
       </c>
       <c r="M118" t="n">
         <v>11.584607</v>
       </c>
-      <c r="N118" t="inlineStr"/>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B119" t="inlineStr">
@@ -6993,7 +6971,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
       <c r="L119" t="n">
         <v>45.7669109</v>
       </c>
@@ -7007,7 +6984,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B120" t="inlineStr">
@@ -7020,7 +6997,6 @@
           <t>Pipistrellus pipistrellus</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -7049,7 +7025,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
       <c r="L120" t="n">
         <v>45.6348591</v>
       </c>
@@ -7063,7 +7038,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>45572</v>
       </c>
       <c r="B121" t="inlineStr">
@@ -7076,7 +7051,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
           <t>Via lago di fimon 63</t>
@@ -7105,17 +7079,20 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
       <c r="L121" t="n">
         <v>45.4544981</v>
       </c>
       <c r="M121" t="n">
         <v>11.5411704</v>
       </c>
-      <c r="N121" t="inlineStr"/>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>45574</v>
       </c>
       <c r="B122" t="inlineStr">
@@ -7128,7 +7105,6 @@
           <t>Tadarida teniotis</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -7157,7 +7133,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
       <c r="L122" t="n">
         <v>45.6348591</v>
       </c>
@@ -7171,7 +7146,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>45583</v>
       </c>
       <c r="B123" t="inlineStr">
@@ -7184,7 +7159,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
           <t>Lonigo</t>
@@ -7213,17 +7187,20 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
       <c r="L123" t="n">
         <v>45.3881155</v>
       </c>
       <c r="M123" t="n">
         <v>11.38799</v>
       </c>
-      <c r="N123" t="inlineStr"/>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>45584</v>
       </c>
       <c r="B124" t="inlineStr">
@@ -7269,7 +7246,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
       <c r="L124" t="n">
         <v>45.7113511</v>
       </c>
@@ -7283,7 +7259,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>45586</v>
       </c>
       <c r="B125" t="inlineStr">
@@ -7296,7 +7272,6 @@
           <t>Pipistrello</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -7325,7 +7300,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
       <c r="L125" t="n">
         <v>45.6348591</v>
       </c>
@@ -7339,7 +7313,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>45591</v>
       </c>
       <c r="B126" t="inlineStr">
@@ -7385,7 +7359,6 @@
           <t>liberato</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
       <c r="L126" t="n">
         <v>45.5422473</v>
       </c>
@@ -7399,7 +7372,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>45599</v>
       </c>
       <c r="B127" t="inlineStr">
@@ -7412,7 +7385,6 @@
           <t>Hypsugo savii</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
           <t>Vicenza</t>
@@ -7441,7 +7413,6 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
       <c r="L127" t="n">
         <v>45.6348591</v>
       </c>
@@ -7455,7 +7426,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>45607</v>
       </c>
       <c r="B128" t="inlineStr">
@@ -7501,17 +7472,20 @@
           <t>morto</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
       <c r="L128" t="n">
         <v>45.4976786</v>
       </c>
       <c r="M128" t="n">
         <v>11.5381176</v>
       </c>
-      <c r="N128" t="inlineStr"/>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B129" t="inlineStr">
@@ -7557,7 +7531,6 @@
           <t>in degenza</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
       <c r="L129" t="n">
         <v>45.5468804</v>
       </c>

--- a/web/Pipistrelli 2024.xlsx
+++ b/web/Pipistrelli 2024.xlsx
@@ -582,7 +582,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>vicenza</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cornedo Vicentino</t>
+          <t>Cornedo vicentino</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bassano del Grappa</t>
+          <t>Bassano del grappa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Altavilla Vicentina </t>
+          <t>Altavilla vicentina</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bassano del Grappa </t>
+          <t>Bassano del grappa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Monticello Conte Otto</t>
+          <t>Monticello conte otto</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Piovene Rocchette</t>
+          <t>Piovene rocchette</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>arcugnano</t>
+          <t>Arcugnano</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">montecchio </t>
+          <t>Montecchio maggiore</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2442,10 +2442,10 @@
         <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>42.663533</v>
+        <v>45.5479</v>
       </c>
       <c r="M34" t="n">
-        <v>12.286862</v>
+        <v>11.5446</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>VI</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Camisano Vicentino</t>
+          <t>Camisano vicentino</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Camisano Vicentino</t>
+          <t>Camisano vicentino</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Pove del Grappa</t>
+          <t>Pove del grappa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thiene </t>
+          <t>Thiene</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tezze sul Brenta </t>
+          <t>Tezze sul brenta</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>altavilla vicentina</t>
+          <t>Altavilla vicentina</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>brogliano</t>
+          <t>Brogliano</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isola Vicentina </t>
+          <t>Isola vicentina</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>altavilla vicentina</t>
+          <t>Altavilla vicentina</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>vicenza</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>vicenza</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4926,10 +4926,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>45.443275</v>
+        <v>45.1332</v>
       </c>
       <c r="M76" t="n">
-        <v>9.745760000000001</v>
+        <v>10.0213</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
@@ -5168,10 +5168,10 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>45.5208426</v>
+        <v>45.1332</v>
       </c>
       <c r="M80" t="n">
-        <v>11.6905167</v>
+        <v>10.0213</v>
       </c>
       <c r="N80" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Montecchio</t>
+          <t>Montecchio maggiore</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>VI</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Altavilla</t>
+          <t>Altavilla vicentina</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -6182,6 +6182,11 @@
         <v>11.463433</v>
       </c>
       <c r="N97" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
         <is>
           <t>VI</t>
         </is>
@@ -6289,10 +6294,10 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>47.2186371</v>
+        <v>45.5479</v>
       </c>
       <c r="M99" t="n">
-        <v>-1.5541362</v>
+        <v>11.5446</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
@@ -6331,7 +6336,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Romano d'Ezzelino</t>
+          <t>Romano d'ezzelino</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -6572,7 +6577,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bassano del Grappa </t>
+          <t>Bassano del grappa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6631,7 +6636,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Barbarano Mossano</t>
+          <t>Barbarano mossano</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7052,7 +7057,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bassano del Grappa</t>
+          <t>Bassano del grappa</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -7278,7 +7283,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dueville </t>
+          <t>Dueville</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -7406,7 +7411,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Monticello Conte Otto</t>
+          <t>Monticello conte otto</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -7470,7 +7475,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Bassano del Grappa</t>
+          <t>Bassano del grappa</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">

--- a/web/Pipistrelli 2024.xlsx
+++ b/web/Pipistrelli 2024.xlsx
@@ -769,7 +769,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cornedo vicentino</t>
+          <t>Cornedo Vicentino</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cornedo vicentino</t>
+          <t>Cornedo Vicentino</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bassano del grappa</t>
+          <t>Bassano Del Grappa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Altavilla vicentina</t>
+          <t>Altavilla Vicentina</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grisignano </t>
+          <t>Grisignano Di Zocco</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1042,10 +1042,15 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>44.1821589</v>
+        <v>45.5479</v>
       </c>
       <c r="M10" t="n">
-        <v>12.0321866</v>
+        <v>11.5446</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1197,7 +1202,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bassano del grappa</t>
+          <t>Bassano Del Grappa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1708,7 +1713,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grisignano</t>
+          <t>Grisignano Di Zocco</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1730,10 +1735,15 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>44.1821589</v>
+        <v>45.5479</v>
       </c>
       <c r="M22" t="n">
-        <v>12.0321866</v>
+        <v>11.5446</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -2119,7 +2129,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Monticello conte otto</t>
+          <t>Monticello Conte Otto</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2237,7 +2247,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Piovene rocchette</t>
+          <t>Piovene Rocchette</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2417,7 +2427,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Montecchio maggiore</t>
+          <t>Montecchio Maggiore</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2484,7 +2494,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Camisano vicentino</t>
+          <t>Camisano Vicentino</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2548,7 +2558,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Camisano vicentino</t>
+          <t>Camisano Vicentino</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2888,7 +2898,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Pove del grappa</t>
+          <t>Pove Del Grappa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3122,7 +3132,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Isola vicentina</t>
+          <t>Isola Vicentina</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3534,7 +3544,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tezze sul brenta</t>
+          <t>Tezze Sul Brenta</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3778,7 +3788,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Altavilla vicentina</t>
+          <t>Altavilla Vicentina</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3964,7 +3974,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grisignano</t>
+          <t>Grisignano Di Zocco</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3989,10 +3999,15 @@
         <v>1</v>
       </c>
       <c r="L60" t="n">
-        <v>44.1821589</v>
+        <v>45.5479</v>
       </c>
       <c r="M60" t="n">
-        <v>12.0321866</v>
+        <v>11.5446</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>VI</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -4075,7 +4090,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Isola vicentina</t>
+          <t>Isola Vicentina</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4311,7 +4326,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Altavilla vicentina</t>
+          <t>Altavilla Vicentina</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4668,7 +4683,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Altavilla vicentina</t>
+          <t>Altavilla Vicentina</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4904,7 +4919,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Camisano</t>
+          <t>Camisano Vicentino</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4926,10 +4941,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>45.1332</v>
+        <v>45.5479</v>
       </c>
       <c r="M76" t="n">
-        <v>10.0213</v>
+        <v>11.5446</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
@@ -4938,7 +4953,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>VI</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5161,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Camisano</t>
+          <t>Camisano Vicentino</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5168,10 +5183,10 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>45.1332</v>
+        <v>45.5479</v>
       </c>
       <c r="M80" t="n">
-        <v>10.0213</v>
+        <v>11.5446</v>
       </c>
       <c r="N80" t="inlineStr">
         <is>
@@ -5180,7 +5195,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>VI</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5279,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cornedo vicentino</t>
+          <t>Cornedo Vicentino</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -5632,7 +5647,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Pove del grappa</t>
+          <t>Pove Del Grappa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5750,7 +5765,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Montecchio maggiore</t>
+          <t>Montecchio Maggiore</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5812,7 +5827,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bassano del grappa</t>
+          <t>Bassano Del Grappa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5930,7 +5945,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bassano del grappa</t>
+          <t>Bassano Del Grappa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6154,7 +6169,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Altavilla vicentina</t>
+          <t>Altavilla Vicentina</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -6336,7 +6351,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Romano d'ezzelino</t>
+          <t>Romano D'Ezzelino</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -6454,7 +6469,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Pove del grappa</t>
+          <t>Pove Del Grappa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6577,7 +6592,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bassano del grappa</t>
+          <t>Bassano Del Grappa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6636,7 +6651,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Barbarano mossano</t>
+          <t>Barbarano Mossano</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7057,7 +7072,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bassano del grappa</t>
+          <t>Bassano Del Grappa</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -7411,7 +7426,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Monticello conte otto</t>
+          <t>Monticello Conte Otto</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -7475,7 +7490,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Bassano del grappa</t>
+          <t>Bassano Del Grappa</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
